--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,130 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/108719960</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136905954</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännås, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>334763</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6387017</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kerstin Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kerstin Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136905954</t>
         </is>
       </c>
     </row>
@@ -908,6 +1032,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136905954</v>
       </c>
       <c r="B4" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136905954</v>
       </c>
       <c r="B4" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -941,11 +941,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136905954</v>
       </c>
       <c r="B4" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>136905954</v>
       </c>
       <c r="B4" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
